--- a/data/trans_bre/P1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 5,93</t>
+          <t>-0,31; 6,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,51</t>
+          <t>-0,66; 7,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 5,63</t>
+          <t>-1,47; 5,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 4,79</t>
+          <t>-2,09; 4,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,91; 181,45</t>
+          <t>-7,14; 222,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,04; 202,09</t>
+          <t>-16,0; 234,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,94; 161,6</t>
+          <t>-26,19; 170,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,24; 117,43</t>
+          <t>-30,5; 126,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 8,02</t>
+          <t>0,33; 7,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 6,86</t>
+          <t>-1,71; 6,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 5,08</t>
+          <t>-2,26; 4,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,38</t>
+          <t>3,58; 9,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 266,08</t>
+          <t>3,31; 304,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-25,36; 149,04</t>
+          <t>-21,97; 159,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 158,02</t>
+          <t>-38,42; 121,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>89,64; 601,27</t>
+          <t>78,96; 577,79</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,36</t>
+          <t>0,22; 10,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,07; 15,14</t>
+          <t>4,51; 15,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 13,45</t>
+          <t>1,43; 14,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,82</t>
+          <t>1,15; 12,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 203,02</t>
+          <t>1,42; 208,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>36,96; 207,58</t>
+          <t>43,81; 209,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 245,24</t>
+          <t>16,82; 247,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 491,59</t>
+          <t>9,37; 627,81</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 4,75</t>
+          <t>-0,83; 4,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,37</t>
+          <t>0,51; 6,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 8,74</t>
+          <t>3,54; 8,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,09</t>
+          <t>-3,3; 3,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 69,05</t>
+          <t>-10,33; 65,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 81,88</t>
+          <t>5,12; 83,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,97; 177,25</t>
+          <t>49,47; 181,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-43,17; 52,45</t>
+          <t>-44,98; 53,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 7,11</t>
+          <t>-0,54; 6,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,72</t>
+          <t>10,78; 18,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,9; 11,76</t>
+          <t>4,99; 12,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,71</t>
+          <t>0,73; 8,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 169,71</t>
+          <t>-7,1; 168,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>140,5; 442,77</t>
+          <t>138,75; 449,91</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,65; 173,81</t>
+          <t>46,1; 169,48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,43; 128,84</t>
+          <t>9,51; 131,13</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 8,55</t>
+          <t>2,85; 8,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,29; 14,93</t>
+          <t>8,28; 14,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,95; 12,29</t>
+          <t>6,03; 12,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 14,64</t>
+          <t>6,45; 14,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,86; 458,6</t>
+          <t>42,5; 367,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>111,91; 826,56</t>
+          <t>116,15; 773,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>97,31; 645,55</t>
+          <t>99,12; 659,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>60,64; 825,03</t>
+          <t>66,8; 861,54</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,73</t>
+          <t>2,1; 4,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,09; 9,17</t>
+          <t>6,07; 9,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,71</t>
+          <t>4,75; 7,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 6,71</t>
+          <t>3,02; 6,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,02; 86,03</t>
+          <t>30,43; 84,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,93; 143,04</t>
+          <t>77,65; 142,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,86; 140,65</t>
+          <t>69,82; 139,17</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,37; 144,26</t>
+          <t>51,54; 144,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P1001-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1001-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 6,28</t>
+          <t>-0,83; 6,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 7,16</t>
+          <t>-0,46; 7,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,57</t>
+          <t>-1,59; 5,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,94</t>
+          <t>-0,86; 5,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 222,98</t>
+          <t>-18,99; 218,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 234,69</t>
+          <t>-14,38; 237,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,19; 170,83</t>
+          <t>-26,5; 158,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 126,25</t>
+          <t>-14,87; 138,08</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,89</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>255,26%</t>
+          <t>249,35%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 7,88</t>
+          <t>0,71; 7,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,98</t>
+          <t>-1,48; 6,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,67</t>
+          <t>-1,95; 5,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,58; 9,79</t>
+          <t>4,04; 10,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,31; 304,73</t>
+          <t>6,3; 283,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-21,97; 159,69</t>
+          <t>-20,4; 151,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 121,42</t>
+          <t>-31,13; 157,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,96; 577,79</t>
+          <t>92,17; 643,65</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>105,07%</t>
+          <t>41,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 10,49</t>
+          <t>0,06; 10,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 15,48</t>
+          <t>4,29; 15,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 14,12</t>
+          <t>1,36; 14,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 12,42</t>
+          <t>-0,89; 7,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 208,56</t>
+          <t>-5,38; 206,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,81; 209,68</t>
+          <t>43,25; 217,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,82; 247,34</t>
+          <t>13,27; 254,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,37; 627,81</t>
+          <t>-10,95; 136,66</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,38</t>
+          <t>2,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 4,44</t>
+          <t>-0,79; 4,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,36</t>
+          <t>0,68; 6,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,54; 8,85</t>
+          <t>3,2; 8,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 3,13</t>
+          <t>-0,07; 4,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 65,78</t>
+          <t>-8,95; 69,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,12; 83,56</t>
+          <t>6,55; 85,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,47; 181,81</t>
+          <t>48,59; 185,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-44,98; 53,18</t>
+          <t>-1,11; 79,61</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,07</t>
+          <t>7,24</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 6,85</t>
+          <t>-0,24; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,78; 18,02</t>
+          <t>11,12; 18,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,99; 12,0</t>
+          <t>4,24; 11,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,59</t>
+          <t>4,21; 10,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 168,01</t>
+          <t>-5,81; 155,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>138,75; 449,91</t>
+          <t>139,88; 462,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,1; 169,48</t>
+          <t>40,62; 167,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 131,13</t>
+          <t>44,1; 174,34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11,44</t>
+          <t>10,4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>300,6%</t>
+          <t>230,68%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,48</t>
+          <t>2,97; 8,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,28; 14,73</t>
+          <t>8,62; 15,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,15</t>
+          <t>6,22; 12,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 14,74</t>
+          <t>4,21; 13,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>42,5; 367,26</t>
+          <t>46,47; 416,68</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>116,15; 773,39</t>
+          <t>129,85; 832,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99,12; 659,87</t>
+          <t>99,43; 595,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>66,8; 861,54</t>
+          <t>34,47; 627,05</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,04</t>
+          <t>5,64</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>94,85%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,59</t>
+          <t>1,91; 4,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,07</t>
+          <t>6,07; 9,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 7,56</t>
+          <t>4,93; 7,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,78</t>
+          <t>4,25; 6,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,43; 84,82</t>
+          <t>29,36; 82,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,65; 142,29</t>
+          <t>77,1; 140,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,82; 139,17</t>
+          <t>74,96; 144,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,54; 144,01</t>
+          <t>64,02; 132,21</t>
         </is>
       </c>
     </row>
